--- a/config/auto_configs/2009_Hyundai_Hyundai_Genesis(BH)_G 3.3 MPI.xlsx
+++ b/config/auto_configs/2009_Hyundai_Hyundai_Genesis(BH)_G 3.3 MPI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_00260</t>
+          <t>HMA_0015C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C1275</t>
+          <t>P0315</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_00260</t>
+          <t>HMA_0015C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C1358</t>
+          <t>P0340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_00260</t>
+          <t>HMA_0015C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C1613</t>
+          <t>P0616</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,20 +586,1428 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P0617</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P0750</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P0755</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P0760</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P0765</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P0770</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P1523</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P1607</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P1691</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P2197</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P2198</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P2272</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P2273</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P2502</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P2610</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_0015C</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U0104</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P0751</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P0752</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P0756</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P0757</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P0761</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P0762</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P0766</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P0976</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P0977</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P0979</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P0980</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P0982</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P0983</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P0985</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P0986</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P2762</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P2763</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P2764</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HMA_0015D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>U0122</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>ESC</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>HMA_00260</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C1275</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ESC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HMA_00260</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C1358</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ESC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HMA_00260</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>C1613</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ESC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HMA_00260</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>C1638</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HMA_0015F</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HMA_0011A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HMA_00141</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HMA_00149</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AFLS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HMA_0015B</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AHLS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HMA_00154</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HMA_0014C</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DDM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HMA_00148</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ECW</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HMA_00150</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EPB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HMA_000FE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HMA_0015E</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HMA_00147</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FBWS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HMA_0014F</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HMA_00107</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IMM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HMA_00029</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IPM</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HMA_00146</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IPM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HMA_00145</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HMA_0014D</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PDM</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HMA_00151</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HMA_0014E</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HMA_0014B</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HMA_00153</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HMA_00068</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TUNER</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HMA_00108</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>User Option</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HMA_0010E</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VRS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HMA_00109</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>00</t>
         </is>
